--- a/Orbital Mechanics/Project/Code/Assignment2/to choose.xlsx
+++ b/Orbital Mechanics/Project/Code/Assignment2/to choose.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\a1pab\Desktop\1POLIMI\polimiCode\Orbital Mechanics\Project\Code\Assignment2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D90811F6-3F45-46DD-953C-068C3E9076D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C308984-5210-4027-8038-129E7E87397C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{212F7127-6FB2-4D2E-973F-A841FD98D95E}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4474" uniqueCount="1546">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4458" uniqueCount="1545">
   <si>
     <t>ARIANE 5 R/B</t>
   </si>
@@ -4670,16 +4670,13 @@
     <t>TLE</t>
   </si>
   <si>
-    <t>https://celestrak.org/NORAD/elements/gp.php?CATNR=10485</t>
-  </si>
-  <si>
-    <t>https://celestrak.org/NORAD/elements/gp.php?CATNR=10998</t>
-  </si>
-  <si>
-    <t>https://celestrak.org/NORAD/elements/gp.php?CATNR=13016</t>
-  </si>
-  <si>
     <t>https://celestrak.org/NORAD/elements/gp.php?CATNR=25850</t>
+  </si>
+  <si>
+    <t>tracking</t>
+  </si>
+  <si>
+    <t>https://www.satview.org/?sat_id=25850U</t>
   </si>
 </sst>
 </file>
@@ -4894,7 +4891,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -4945,6 +4942,7 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -35021,7 +35019,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37DCD7B9-B6B5-4EE7-8015-9BDC4274F80D}">
-  <dimension ref="A1:J26"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:10">
@@ -35047,200 +35045,70 @@
         <v>979</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
-      <c r="A2" s="5"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="6"/>
+    <row r="2" spans="1:10" ht="21">
+      <c r="A2" s="5" t="s">
+        <v>376</v>
+      </c>
+      <c r="B2" s="1">
+        <v>1999</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>552</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="E2" s="1">
+        <v>40601</v>
+      </c>
+      <c r="F2" s="1">
+        <v>459</v>
+      </c>
+      <c r="G2" s="1">
+        <v>732</v>
+      </c>
+      <c r="H2" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="I2" t="s">
+        <v>1541</v>
+      </c>
+      <c r="J2" s="18" t="s">
+        <v>1542</v>
+      </c>
     </row>
     <row r="3" spans="1:10">
-      <c r="A3" s="5"/>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="6"/>
-    </row>
-    <row r="4" spans="1:10" ht="21">
-      <c r="A4" s="5" t="s">
-        <v>376</v>
-      </c>
-      <c r="B4" s="1">
-        <v>1999</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>552</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="E4" s="1">
-        <v>40601</v>
-      </c>
-      <c r="F4" s="1">
-        <v>459</v>
-      </c>
-      <c r="G4" s="1">
-        <v>732</v>
-      </c>
-      <c r="H4" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="I4" t="s">
-        <v>1541</v>
-      </c>
-      <c r="J4" t="s">
-        <v>1545</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
-      <c r="A5" s="5"/>
-      <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
-      <c r="H5" s="6"/>
-    </row>
-    <row r="6" spans="1:10" ht="21">
-      <c r="A6" s="5" t="s">
-        <v>376</v>
-      </c>
-      <c r="B6" s="1">
-        <v>1981</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>850</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>752</v>
-      </c>
-      <c r="E6" s="1">
-        <v>33874</v>
-      </c>
-      <c r="F6" s="1">
-        <v>462</v>
-      </c>
-      <c r="G6" s="1">
-        <v>599</v>
-      </c>
-      <c r="H6" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="I6" t="s">
-        <v>1541</v>
-      </c>
-      <c r="J6" t="s">
+      <c r="I3" t="s">
+        <v>1543</v>
+      </c>
+      <c r="J3" t="s">
         <v>1544</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="21">
-      <c r="A7" s="5" t="s">
-        <v>376</v>
-      </c>
-      <c r="B7" s="1">
-        <v>1978</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>881</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>752</v>
-      </c>
-      <c r="E7" s="1">
-        <v>40015</v>
-      </c>
-      <c r="F7" s="1">
-        <v>457</v>
-      </c>
-      <c r="G7" s="1">
-        <v>720</v>
-      </c>
-      <c r="H7" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="I7" t="s">
-        <v>1541</v>
-      </c>
-      <c r="J7" t="s">
-        <v>1543</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="21">
-      <c r="A8" s="5" t="s">
-        <v>376</v>
-      </c>
-      <c r="B8" s="1">
-        <v>1977</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>890</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="E8" s="1">
-        <v>40484</v>
-      </c>
-      <c r="F8" s="1">
-        <v>470</v>
-      </c>
-      <c r="G8" s="1">
-        <v>730</v>
-      </c>
-      <c r="H8" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="I8" t="s">
-        <v>1541</v>
-      </c>
-      <c r="J8" t="s">
-        <v>1542</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10">
-      <c r="A9" s="5"/>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
-      <c r="H9" s="6"/>
-    </row>
-    <row r="25" spans="2:8">
-      <c r="B25" s="16"/>
-      <c r="C25" s="17"/>
-      <c r="D25" s="17"/>
-      <c r="E25" s="17"/>
-      <c r="F25" s="17"/>
-      <c r="G25" s="17"/>
-      <c r="H25" s="17"/>
-    </row>
-    <row r="26" spans="2:8">
-      <c r="B26" s="16"/>
-      <c r="C26" s="17"/>
-      <c r="D26" s="17"/>
-      <c r="E26" s="17"/>
-      <c r="F26" s="17"/>
-      <c r="G26" s="17"/>
-      <c r="H26" s="17"/>
+    <row r="18" spans="2:8">
+      <c r="B18" s="16"/>
+      <c r="C18" s="17"/>
+      <c r="D18" s="17"/>
+      <c r="E18" s="17"/>
+      <c r="F18" s="17"/>
+      <c r="G18" s="17"/>
+      <c r="H18" s="17"/>
+    </row>
+    <row r="19" spans="2:8">
+      <c r="B19" s="16"/>
+      <c r="C19" s="17"/>
+      <c r="D19" s="17"/>
+      <c r="E19" s="17"/>
+      <c r="F19" s="17"/>
+      <c r="G19" s="17"/>
+      <c r="H19" s="17"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="H4" r:id="rId1" display="https://www.satview.org/?sat_id=25850U" xr:uid="{D524FBC5-7515-43A2-B8EF-727558C70D97}"/>
-    <hyperlink ref="H6" r:id="rId2" display="https://www.satview.org/?sat_id=13016U" xr:uid="{9A3F116F-C8DF-49CF-B12C-4FECF9F24D53}"/>
-    <hyperlink ref="H7" r:id="rId3" display="https://www.satview.org/?sat_id=10998U" xr:uid="{834CB3C0-4B20-446E-92D9-AE7D0DA2C256}"/>
-    <hyperlink ref="H8" r:id="rId4" display="https://www.satview.org/?sat_id=10485U" xr:uid="{E5D7DB0F-63AE-4D47-A437-493E34D16805}"/>
+    <hyperlink ref="H2" r:id="rId1" display="https://www.satview.org/?sat_id=25850U" xr:uid="{D524FBC5-7515-43A2-B8EF-727558C70D97}"/>
+    <hyperlink ref="J2" r:id="rId2" xr:uid="{24C484CC-642E-4DF1-9E11-CDAD4B98DC33}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId5"/>
+  <pageSetup orientation="portrait" r:id="rId3"/>
 </worksheet>
 </file>
--- a/Orbital Mechanics/Project/Code/Assignment2/to choose.xlsx
+++ b/Orbital Mechanics/Project/Code/Assignment2/to choose.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\a1pab\Desktop\1POLIMI\polimiCode\Orbital Mechanics\Project\Code\Assignment2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C308984-5210-4027-8038-129E7E87397C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04EFF87C-F8D4-4F64-8FFE-18DCBC3FDF8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{212F7127-6FB2-4D2E-973F-A841FD98D95E}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4458" uniqueCount="1545">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4479" uniqueCount="1566">
   <si>
     <t>ARIANE 5 R/B</t>
   </si>
@@ -4677,13 +4677,76 @@
   </si>
   <si>
     <t>https://www.satview.org/?sat_id=25850U</t>
+  </si>
+  <si>
+    <t>Blok-ML (Molniya-M Blok-ML)</t>
+  </si>
+  <si>
+    <t>1999-036D</t>
+  </si>
+  <si>
+    <t>Rocket Body</t>
+  </si>
+  <si>
+    <t>Cyl</t>
+  </si>
+  <si>
+    <t>from https://discosweb.esoc.esa.int/objects?page=259&amp;pageSize=100</t>
+  </si>
+  <si>
+    <t>NAME</t>
+  </si>
+  <si>
+    <t>DISCOS ID</t>
+  </si>
+  <si>
+    <t>SATNO</t>
+  </si>
+  <si>
+    <t>COSPAR ID</t>
+  </si>
+  <si>
+    <t>OBJECT CLASS</t>
+  </si>
+  <si>
+    <t>SHAPE</t>
+  </si>
+  <si>
+    <t>HEIGHT (m)</t>
+  </si>
+  <si>
+    <t>MASS (kg)</t>
+  </si>
+  <si>
+    <t>WIDTH (m)</t>
+  </si>
+  <si>
+    <t>MAX CROSS SECTION (m^2)</t>
+  </si>
+  <si>
+    <t>AVG CROSS SECTION (m^2)</t>
+  </si>
+  <si>
+    <t>MIN CROSS SECTION (m^2)</t>
+  </si>
+  <si>
+    <t>RADAR CROSS SECTION (m^2)</t>
+  </si>
+  <si>
+    <t>https://www.n2yo.com/satellite/?s=25850#results</t>
+  </si>
+  <si>
+    <t>https://apps.dtic.mil/sti/pdfs/ADA395503.pdf</t>
+  </si>
+  <si>
+    <t>cd Drag</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4721,6 +4784,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -4891,7 +4960,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -4943,6 +5012,9 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -35019,8 +35091,11 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37DCD7B9-B6B5-4EE7-8015-9BDC4274F80D}">
-  <dimension ref="A1:J19"/>
+  <dimension ref="A1:J23"/>
   <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="30" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" t="s">
@@ -35045,7 +35120,7 @@
         <v>979</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="21">
+    <row r="2" spans="1:10">
       <c r="A2" s="5" t="s">
         <v>376</v>
       </c>
@@ -35085,8 +35160,81 @@
         <v>1544</v>
       </c>
     </row>
-    <row r="18" spans="2:8">
-      <c r="B18" s="16"/>
+    <row r="11" spans="1:10">
+      <c r="A11" t="s">
+        <v>1549</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="16.5">
+      <c r="A12" s="19">
+        <v>25847</v>
+      </c>
+      <c r="B12" t="s">
+        <v>1551</v>
+      </c>
+      <c r="F12" t="s">
+        <v>1563</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="16.5">
+      <c r="A13" s="19" t="s">
+        <v>1545</v>
+      </c>
+      <c r="B13" t="s">
+        <v>1550</v>
+      </c>
+      <c r="F13">
+        <v>2</v>
+      </c>
+      <c r="G13" t="s">
+        <v>1562</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="16.5">
+      <c r="A14" s="19">
+        <v>25850</v>
+      </c>
+      <c r="B14" t="s">
+        <v>1552</v>
+      </c>
+      <c r="F14" t="s">
+        <v>1564</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="16.5">
+      <c r="A15" s="19" t="s">
+        <v>1546</v>
+      </c>
+      <c r="B15" t="s">
+        <v>1553</v>
+      </c>
+      <c r="F15" t="s">
+        <v>1565</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="16.5">
+      <c r="A16" s="19" t="s">
+        <v>1547</v>
+      </c>
+      <c r="B16" t="s">
+        <v>1554</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="16.5">
+      <c r="A17" s="19">
+        <v>900</v>
+      </c>
+      <c r="B17" t="s">
+        <v>1557</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="16.5">
+      <c r="A18" s="19" t="s">
+        <v>1548</v>
+      </c>
+      <c r="B18" s="16" t="s">
+        <v>1555</v>
+      </c>
       <c r="C18" s="17"/>
       <c r="D18" s="17"/>
       <c r="E18" s="17"/>
@@ -35094,14 +35242,51 @@
       <c r="G18" s="17"/>
       <c r="H18" s="17"/>
     </row>
-    <row r="19" spans="2:8">
-      <c r="B19" s="16"/>
+    <row r="19" spans="1:8" ht="16.5">
+      <c r="A19" s="19">
+        <v>2.6</v>
+      </c>
+      <c r="B19" s="16" t="s">
+        <v>1556</v>
+      </c>
       <c r="C19" s="17"/>
       <c r="D19" s="17"/>
       <c r="E19" s="17"/>
       <c r="F19" s="17"/>
       <c r="G19" s="17"/>
       <c r="H19" s="17"/>
+    </row>
+    <row r="20" spans="1:8" ht="16.5">
+      <c r="A20" s="19">
+        <v>2.58</v>
+      </c>
+      <c r="B20" t="s">
+        <v>1558</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="16.5">
+      <c r="A21" s="19">
+        <v>8.5046138566544798</v>
+      </c>
+      <c r="B21" t="s">
+        <v>1559</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="16.5">
+      <c r="A22" s="19">
+        <v>5.2279243348387796</v>
+      </c>
+      <c r="B22" t="s">
+        <v>1561</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="16.5">
+      <c r="A23" s="19">
+        <v>7.8824130474894698</v>
+      </c>
+      <c r="B23" t="s">
+        <v>1560</v>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>

--- a/Orbital Mechanics/Project/Code/Assignment2/to choose.xlsx
+++ b/Orbital Mechanics/Project/Code/Assignment2/to choose.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\a1pab\Desktop\1POLIMI\polimiCode\Orbital Mechanics\Project\Code\Assignment2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04EFF87C-F8D4-4F64-8FFE-18DCBC3FDF8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCC281EC-B7D7-40A1-84B6-7570F7CCFF15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{212F7127-6FB2-4D2E-973F-A841FD98D95E}"/>
   </bookViews>
@@ -35197,9 +35197,6 @@
       <c r="B14" t="s">
         <v>1552</v>
       </c>
-      <c r="F14" t="s">
-        <v>1564</v>
-      </c>
     </row>
     <row r="15" spans="1:10" ht="16.5">
       <c r="A15" s="19" t="s">
@@ -35208,9 +35205,6 @@
       <c r="B15" t="s">
         <v>1553</v>
       </c>
-      <c r="F15" t="s">
-        <v>1565</v>
-      </c>
     </row>
     <row r="16" spans="1:10" ht="16.5">
       <c r="A16" s="19" t="s">
@@ -35227,6 +35221,9 @@
       <c r="B17" t="s">
         <v>1557</v>
       </c>
+      <c r="F17" t="s">
+        <v>1564</v>
+      </c>
     </row>
     <row r="18" spans="1:8" ht="16.5">
       <c r="A18" s="19" t="s">
@@ -35238,7 +35235,9 @@
       <c r="C18" s="17"/>
       <c r="D18" s="17"/>
       <c r="E18" s="17"/>
-      <c r="F18" s="17"/>
+      <c r="F18" t="s">
+        <v>1565</v>
+      </c>
       <c r="G18" s="17"/>
       <c r="H18" s="17"/>
     </row>
@@ -35252,7 +35251,9 @@
       <c r="C19" s="17"/>
       <c r="D19" s="17"/>
       <c r="E19" s="17"/>
-      <c r="F19" s="17"/>
+      <c r="F19" s="17">
+        <v>0.89400000000000002</v>
+      </c>
       <c r="G19" s="17"/>
       <c r="H19" s="17"/>
     </row>
